--- a/political_youtube/conflict_over_time/timeline/timeline_overview.xlsx
+++ b/political_youtube/conflict_over_time/timeline/timeline_overview.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Benedikt\PycharmProjects\youtube_data\political_youtube\conflict_over_time\timeline\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PyhcarmProjects\youtube_data\political_youtube\conflict_over_time\timeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9C2FEE-D552-4EE6-9BF3-13699EF0515B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F13531-357E-4324-9DDC-D86B14BA73EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>date</t>
   </si>
@@ -121,6 +118,33 @@
   </si>
   <si>
     <t>Lage im Süden Israels noch nicht unter Kontrolle, Geiseln werden thematisiert, Israel weiter mit massiven Attacken, viele Verwundete und Tote im Gazastreifen. Weiter Raketenangriffe auf Israel. Berichte über Hilfe aus Iran. Berichte über Leichen auf Nova-Festivalgelände</t>
+  </si>
+  <si>
+    <t>Hamas als Terrororganisation</t>
+  </si>
+  <si>
+    <t>Attacke der Hamas, Israel offiziell in Kriegsbereitschaft</t>
+  </si>
+  <si>
+    <t>Solidarität von Scholz und Steinmeier, Aufforderung des UN-Hochkommissars für Menschenrechte (Volker Türk), bei Vergeltungsschlägen zivile Opfer zu vermeiden. EU/NATO sagen, Israel habe Verteidigungsrecht. Solidarität aus USA. Zurückhaltung aus Türkei/Russland/Saudi-Arabien. Katar sieht Israel verantwortlich. Glückwünsche für Hamas von Hisbollah und aus Iran</t>
+  </si>
+  <si>
+    <t>Ägypten bemüht um Deeskalation, Saudi-Arabien sieht Israel mit verantwortlich, pro-palästinensische Demonstrationen im Libanon, in Syrien und Jemen. Irak, Kuwait und Katar geben Israel Schuld</t>
+  </si>
+  <si>
+    <t>Scholz sichert Netanyahu Unterstützung zu. Verurteilt pro-palästinensische Feiern in DE</t>
+  </si>
+  <si>
+    <t>Bericht über 700 israelische Opfer, 2243 Verletzte, über 100 Geiseln. Kriegszustand ausgerufen.</t>
+  </si>
+  <si>
+    <t>Bericht über Unterstützung der Hamas aus Iran</t>
+  </si>
+  <si>
+    <t>USA verlegen Kriegsschiffe und Kampfjets in die Region.</t>
+  </si>
+  <si>
+    <t>Weitere Kämpfe in israelischem Grenzgebiet und im Gazastreifen. Intensivierung israelischer Luftangriffe auf den Gazastreifen. UN gibt an, Israel habe bereits 159 Wohneinheiten zerstört und 1210 weitere schwer beschädigt.</t>
   </si>
 </sst>
 </file>
@@ -445,14 +469,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F28"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" style="1" customWidth="1"/>
-    <col min="2" max="2" width="69.42578125" customWidth="1"/>
+    <col min="2" max="2" width="69.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -460,7 +484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -468,7 +492,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -476,7 +500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
@@ -484,7 +508,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -492,109 +516,140 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F20" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F21" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F22" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F23" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F24" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="F25" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>27</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F27" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F28" s="1" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
